--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -1,25 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GF_X\AAAGameData\DataTables\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="2775" windowWidth="25860" windowHeight="14685"/>
+    <workbookView windowWidth="19200" windowHeight="8200"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="47">
   <si>
     <t>#</t>
   </si>
@@ -27,16 +35,37 @@
     <t>关卡表</t>
   </si>
   <si>
+    <t>i18n</t>
+  </si>
+  <si>
     <t>ID</t>
   </si>
   <si>
-    <t>LvPfbName</t>
-  </si>
-  <si>
-    <t>InitMoney</t>
-  </si>
-  <si>
-    <t>MoneyColorId</t>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>PrefabPath</t>
+  </si>
+  <si>
+    <t>InitResource</t>
+  </si>
+  <si>
+    <t>NameKey</t>
+  </si>
+  <si>
+    <t>DescKey</t>
+  </si>
+  <si>
+    <t>VictoryConditions</t>
+  </si>
+  <si>
+    <t>VictoryValue</t>
+  </si>
+  <si>
+    <t>LoseConditions</t>
+  </si>
+  <si>
+    <t>LoseValue</t>
   </si>
   <si>
     <t>int</t>
@@ -45,27 +74,14 @@
     <t>string</t>
   </si>
   <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>关卡prefab名</t>
-  </si>
-  <si>
-    <t>玩家初始钱数</t>
-  </si>
-  <si>
-    <t>取值1-6</t>
-  </si>
-  <si>
-    <t>Lv_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LvDisplayName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>s</t>
     </r>
     <r>
@@ -73,44 +89,117 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>tring</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Level.DisplayName1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Level.DisplayName2</t>
-  </si>
-  <si>
-    <t>Level.DisplayName3</t>
-  </si>
-  <si>
-    <t>Level.DisplayName4</t>
-  </si>
-  <si>
-    <t>Level.DisplayName5</t>
-  </si>
-  <si>
-    <t>关卡显示名(多语言)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i18n</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum[]</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>代码内标识符</t>
+  </si>
+  <si>
+    <t>关卡prefab路径</t>
+  </si>
+  <si>
+    <t>初始资源</t>
+  </si>
+  <si>
+    <t>关卡名(多语言)</t>
+  </si>
+  <si>
+    <t>关卡简介(多语言)</t>
+  </si>
+  <si>
+    <t>胜利条件</t>
+  </si>
+  <si>
+    <t>胜利条件设定数值</t>
+  </si>
+  <si>
+    <t>失败条件</t>
+  </si>
+  <si>
+    <t>失败条件设定数值</t>
+  </si>
+  <si>
+    <t>教程关</t>
+  </si>
+  <si>
+    <t>Lv_1</t>
+  </si>
+  <si>
+    <t>Level/Level_Test</t>
+  </si>
+  <si>
+    <t>Lv_Name_1</t>
+  </si>
+  <si>
+    <t>Lv_Desc_1</t>
+  </si>
+  <si>
+    <t>VictoryConditionType.OccupySpecificBuildings</t>
+  </si>
+  <si>
+    <t>FailConditionType.LoseSpecificBuildings</t>
+  </si>
+  <si>
+    <t>Lv_2</t>
+  </si>
+  <si>
+    <t>Lv_Name_2</t>
+  </si>
+  <si>
+    <t>Lv_Desc_2</t>
+  </si>
+  <si>
+    <t>FailConditionType.LoseSpecificBuildings,FailConditionType.ArriveAmountDays</t>
+  </si>
+  <si>
+    <t>Lv_3</t>
+  </si>
+  <si>
+    <t>Lv_Name_3</t>
+  </si>
+  <si>
+    <t>Lv_Desc_3</t>
+  </si>
+  <si>
+    <t>Lv_4</t>
+  </si>
+  <si>
+    <t>Lv_Name_4</t>
+  </si>
+  <si>
+    <t>Lv_Desc_4</t>
+  </si>
+  <si>
+    <t>Lv_5</t>
+  </si>
+  <si>
+    <t>Lv_Name_5</t>
+  </si>
+  <si>
+    <t>Lv_Desc_5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -119,38 +208,351 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="4"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -158,26 +560,331 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFF8CBAD"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8CBAD"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8CBAD"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8CBAD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -435,183 +1142,372 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:R9"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="7" customWidth="1"/>
-    <col min="3" max="3" width="5.125" customWidth="1"/>
-    <col min="4" max="4" width="15.5" customWidth="1"/>
-    <col min="5" max="5" width="14.125" customWidth="1"/>
-    <col min="6" max="6" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5" customWidth="1"/>
+    <col min="4" max="5" width="15.5" customWidth="1"/>
+    <col min="6" max="6" width="14.125" customWidth="1"/>
+    <col min="7" max="8" width="17.5" customWidth="1"/>
+    <col min="9" max="9" width="18.3333333333333" customWidth="1"/>
+    <col min="10" max="12" width="17.8333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" ht="14.75" spans="1:18">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+    </row>
+    <row r="2" ht="14.75" spans="1:18">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+    </row>
+    <row r="3" ht="14.75" spans="1:18">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+    </row>
+    <row r="4" ht="13" customHeight="1" spans="1:18">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="H4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="5" ht="42.75" spans="1:18">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="1">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="G5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+    </row>
+    <row r="6" ht="70.75" spans="1:18">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="1">
+        <v>6</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" s="1">
+        <v>10</v>
+      </c>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+    </row>
+    <row r="7" ht="70.75" spans="1:18">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="1">
+        <v>6</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" s="1">
+        <v>10</v>
+      </c>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+    </row>
+    <row r="8" ht="70.75" spans="1:18">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1">
         <v>4</v>
       </c>
-      <c r="F2" t="s">
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="1">
+        <v>6</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L8" s="1">
+        <v>10</v>
+      </c>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+    </row>
+    <row r="9" ht="70.75" spans="1:18">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1">
         <v>5</v>
       </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="1">
         <v>6</v>
       </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="G9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L9" s="1">
         <v>10</v>
       </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5">
-        <v>200</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6">
-        <v>160</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7">
-        <v>315</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B8">
-        <v>4</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8">
-        <v>210</v>
-      </c>
-      <c r="F8">
-        <v>6</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B9">
-        <v>5</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9">
-        <v>315</v>
-      </c>
-      <c r="F9">
-        <v>3</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="52">
   <si>
     <t>#</t>
   </si>
@@ -47,13 +47,16 @@
     <t>PrefabPath</t>
   </si>
   <si>
+    <t>NameKey</t>
+  </si>
+  <si>
+    <t>DescKey</t>
+  </si>
+  <si>
     <t>InitResource</t>
   </si>
   <si>
-    <t>NameKey</t>
-  </si>
-  <si>
-    <t>DescKey</t>
+    <t>StartPhase</t>
   </si>
   <si>
     <t>VictoryConditions</t>
@@ -96,6 +99,9 @@
     </r>
   </si>
   <si>
+    <t>enum</t>
+  </si>
+  <si>
     <t>enum[]</t>
   </si>
   <si>
@@ -108,13 +114,16 @@
     <t>关卡prefab路径</t>
   </si>
   <si>
+    <t>关卡名(多语言)</t>
+  </si>
+  <si>
+    <t>关卡简介(多语言)</t>
+  </si>
+  <si>
     <t>初始资源</t>
   </si>
   <si>
-    <t>关卡名(多语言)</t>
-  </si>
-  <si>
-    <t>关卡简介(多语言)</t>
+    <t>初始阶段</t>
   </si>
   <si>
     <t>胜利条件</t>
@@ -144,6 +153,9 @@
     <t>Lv_Desc_1</t>
   </si>
   <si>
+    <t>GamePhase.Invade</t>
+  </si>
+  <si>
     <t>VictoryConditionType.OccupySpecificBuildings</t>
   </si>
   <si>
@@ -157,6 +169,9 @@
   </si>
   <si>
     <t>Lv_Desc_2</t>
+  </si>
+  <si>
+    <t>GamePhase.Build</t>
   </si>
   <si>
     <t>FailConditionType.LoseSpecificBuildings,FailConditionType.ArriveAmountDays</t>
@@ -1148,20 +1163,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="7" customWidth="1"/>
     <col min="3" max="3" width="8.5" customWidth="1"/>
     <col min="4" max="5" width="15.5" customWidth="1"/>
-    <col min="6" max="6" width="14.125" customWidth="1"/>
-    <col min="7" max="8" width="17.5" customWidth="1"/>
-    <col min="9" max="9" width="18.3333333333333" customWidth="1"/>
-    <col min="10" max="12" width="17.8333333333333" customWidth="1"/>
+    <col min="6" max="7" width="17.5" customWidth="1"/>
+    <col min="8" max="9" width="14.125" customWidth="1"/>
+    <col min="10" max="10" width="18.3333333333333" customWidth="1"/>
+    <col min="11" max="13" width="17.8333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.75" spans="1:18">
+    <row r="1" ht="14.75" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1171,13 +1186,13 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -1188,8 +1203,9 @@
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
     </row>
-    <row r="2" ht="14.75" spans="1:18">
+    <row r="2" ht="14.75" spans="1:19">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1224,286 +1240,310 @@
       <c r="L2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
     </row>
-    <row r="3" ht="14.75" spans="1:18">
+    <row r="3" ht="14.75" spans="1:19">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="L3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
     </row>
-    <row r="4" ht="13" customHeight="1" spans="1:18">
+    <row r="4" ht="13" customHeight="1" spans="1:19">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
     </row>
-    <row r="5" ht="42.75" spans="1:18">
+    <row r="5" ht="42.75" spans="1:19">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="1">
+        <v>32</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="1">
         <v>0</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="I5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L5" s="1"/>
+        <v>35</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
     </row>
-    <row r="6" ht="70.75" spans="1:18">
+    <row r="6" ht="70.75" spans="1:19">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="1">
+        <v>32</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="1">
         <v>6</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L6" s="1">
+      <c r="K6" s="1"/>
+      <c r="L6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M6" s="1">
         <v>10</v>
       </c>
-      <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
     </row>
-    <row r="7" ht="70.75" spans="1:18">
+    <row r="7" ht="70.75" spans="1:19">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="1">
+        <v>32</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="1">
         <v>6</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="I7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L7" s="1">
+        <v>41</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7" s="1">
         <v>10</v>
       </c>
-      <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
     </row>
-    <row r="8" ht="70.75" spans="1:18">
+    <row r="8" ht="70.75" spans="1:19">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="1">
+        <v>6</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="1">
-        <v>6</v>
-      </c>
-      <c r="G8" s="1" t="s">
+      <c r="J8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L8" s="1">
+      <c r="M8" s="1">
         <v>10</v>
       </c>
-      <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
     </row>
-    <row r="9" ht="70.75" spans="1:18">
+    <row r="9" ht="70.75" spans="1:19">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>5</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="1">
+        <v>32</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="1">
         <v>6</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="I9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L9" s="1">
+        <v>41</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M9" s="1">
         <v>10</v>
       </c>
-      <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="53">
   <si>
     <t>#</t>
   </si>
@@ -144,7 +144,7 @@
     <t>Lv_1</t>
   </si>
   <si>
-    <t>Level/Level_Test</t>
+    <t>Level/Level_1</t>
   </si>
   <si>
     <t>Lv_Name_1</t>
@@ -163,6 +163,9 @@
   </si>
   <si>
     <t>Lv_2</t>
+  </si>
+  <si>
+    <t>Level/Level_2</t>
   </si>
   <si>
     <t>Lv_Name_2</t>
@@ -1391,29 +1394,29 @@
         <v>38</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H6" s="1">
         <v>6</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>36</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M6" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
@@ -1429,32 +1432,32 @@
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H7" s="1">
         <v>6</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>36</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M7" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -1470,29 +1473,29 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H8" s="1">
         <v>6</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>36</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M8" s="1">
         <v>10</v>
@@ -1511,29 +1514,29 @@
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H9" s="1">
         <v>6</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>36</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M9" s="1">
         <v>10</v>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8200"/>
+    <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1364,7 +1364,7 @@
         <v>34</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>35</v>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="54">
   <si>
     <t>#</t>
   </si>
@@ -181,6 +181,9 @@
   </si>
   <si>
     <t>Lv_3</t>
+  </si>
+  <si>
+    <t>Level/Level_3</t>
   </si>
   <si>
     <t>Lv_Name_3</t>
@@ -1416,7 +1419,7 @@
         <v>43</v>
       </c>
       <c r="M6" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
@@ -1435,13 +1438,13 @@
         <v>44</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H7" s="1">
         <v>6</v>
@@ -1473,16 +1476,16 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H8" s="1">
         <v>6</v>
@@ -1514,16 +1517,16 @@
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>39</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H9" s="1">
         <v>6</v>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480"/>
+    <workbookView windowWidth="19200" windowHeight="8200"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1406,7 +1406,7 @@
         <v>41</v>
       </c>
       <c r="H6" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>42</v>
@@ -1447,7 +1447,7 @@
         <v>47</v>
       </c>
       <c r="H7" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>42</v>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8200"/>
+    <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1447,7 +1447,7 @@
         <v>47</v>
       </c>
       <c r="H7" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>42</v>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480"/>
+    <workbookView windowWidth="19200" windowHeight="8200"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1367,7 +1367,7 @@
         <v>34</v>
       </c>
       <c r="H5" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>35</v>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8200"/>
+    <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="55">
   <si>
     <t>#</t>
   </si>
@@ -174,7 +174,7 @@
     <t>Lv_Desc_2</t>
   </si>
   <si>
-    <t>GamePhase.Build</t>
+    <t>GamePhase.BuildBeforeInvade</t>
   </si>
   <si>
     <t>FailConditionType.LoseSpecificBuildings,FailConditionType.ArriveAmountDays</t>
@@ -208,6 +208,9 @@
   </si>
   <si>
     <t>Lv_Desc_5</t>
+  </si>
+  <si>
+    <t>GamePhase.BuildBeforeDefend</t>
   </si>
 </sst>
 </file>
@@ -1532,7 +1535,7 @@
         <v>6</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>36</v>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="78">
   <si>
     <t>#</t>
   </si>
@@ -256,6 +256,9 @@
   </si>
   <si>
     <t>Lv_Desc_3</t>
+  </si>
+  <si>
+    <t>[Unit_BoneButcher,1],[Unit_Intern,5]</t>
   </si>
   <si>
     <t>Lv_4</t>
@@ -1560,7 +1563,7 @@
         <v>64</v>
       </c>
       <c r="M6" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>65</v>
@@ -1603,9 +1606,11 @@
         <v>64</v>
       </c>
       <c r="M7" s="1">
-        <v>8</v>
-      </c>
-      <c r="N7" s="1"/>
+        <v>9</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
@@ -1619,16 +1624,16 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>60</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H8" s="1">
         <v>6</v>
@@ -1644,7 +1649,7 @@
         <v>64</v>
       </c>
       <c r="M8" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
@@ -1660,22 +1665,22 @@
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>60</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H9" s="1">
         <v>6</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>57</v>
@@ -1685,7 +1690,7 @@
         <v>64</v>
       </c>
       <c r="M9" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="83">
   <si>
     <t>#</t>
   </si>
@@ -280,6 +280,21 @@
   </si>
   <si>
     <t>GamePhase.BuildBeforeDefend</t>
+  </si>
+  <si>
+    <t>测试关</t>
+  </si>
+  <si>
+    <t>LvTest</t>
+  </si>
+  <si>
+    <t>Level/LvTest</t>
+  </si>
+  <si>
+    <t>Lv_Name_Test</t>
+  </si>
+  <si>
+    <t>Lv_Desc_Test</t>
   </si>
 </sst>
 </file>
@@ -1239,9 +1254,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
@@ -1699,6 +1714,49 @@
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
     </row>
+    <row r="10" ht="70.75" spans="1:23">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H10" s="1">
+        <v>9</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M10" s="1">
+        <v>9</v>
+      </c>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -243,7 +243,7 @@
     <t>FailConditionType.LoseSpecificBuildings,FailConditionType.ArriveAmountDays</t>
   </si>
   <si>
-    <t>[Unit_BoneButcher,1],[Unit_CanMaker,2]</t>
+    <t>[Unit_BoneButcher,1],[Unit_CanMaker_Lv3,2]</t>
   </si>
   <si>
     <t>Lv_3</t>
@@ -258,7 +258,7 @@
     <t>Lv_Desc_3</t>
   </si>
   <si>
-    <t>[Unit_BoneButcher,1],[Unit_Intern,5]</t>
+    <t>[Unit_BoneButcher_Lv2,1],[Unit_Intern,5]</t>
   </si>
   <si>
     <t>Lv_4</t>
@@ -1254,7 +1254,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:W10"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14"/>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="82">
   <si>
     <t>#</t>
   </si>
@@ -238,9 +238,6 @@
   </si>
   <si>
     <t>GamePhase.BuildBeforeInvade</t>
-  </si>
-  <si>
-    <t>FailConditionType.LoseSpecificBuildings,FailConditionType.ArriveAmountDays</t>
   </si>
   <si>
     <t>[Unit_BoneButcher,1],[Unit_CanMaker_Lv3,2]</t>
@@ -1546,7 +1543,7 @@
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
     </row>
-    <row r="6" ht="70.75" spans="1:23">
+    <row r="6" ht="70" spans="1:23">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>2</v>
@@ -1575,13 +1572,11 @@
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="M6" s="1">
-        <v>7</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
@@ -1589,23 +1584,23 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
     </row>
-    <row r="7" ht="70.75" spans="1:23">
+    <row r="7" ht="70" spans="1:23">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="H7" s="1">
         <v>9</v>
@@ -1618,13 +1613,11 @@
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="M7" s="1">
-        <v>9</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="M7" s="1"/>
       <c r="N7" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
@@ -1632,23 +1625,23 @@
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" ht="70.75" spans="1:23">
+    <row r="8" ht="42.75" spans="1:23">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>60</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="H8" s="1">
         <v>6</v>
@@ -1661,11 +1654,9 @@
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="M8" s="1">
-        <v>11</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
@@ -1673,40 +1664,38 @@
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" ht="70.75" spans="1:23">
+    <row r="9" ht="42.75" spans="1:23">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>5</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>60</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="H9" s="1">
         <v>6</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>57</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="M9" s="1">
-        <v>12</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
@@ -1720,22 +1709,22 @@
         <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="H10" s="1">
-        <v>9</v>
+        <v>200</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>63</v>
@@ -1745,12 +1734,12 @@
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="M10" s="1">
-        <v>9</v>
-      </c>
-      <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\Avenge\AAAGameData\DataTables\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="83">
   <si>
     <t>#</t>
   </si>
@@ -292,6 +297,9 @@
   </si>
   <si>
     <t>Lv_Desc_Test</t>
+  </si>
+  <si>
+    <t>[Unit_BoneButcher,1],[Unit_RiotGuard_Lv3,2]</t>
   </si>
 </sst>
 </file>
@@ -1543,7 +1551,7 @@
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
     </row>
-    <row r="6" ht="70" spans="1:23">
+    <row r="6" ht="70.75" spans="1:23">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>2</v>
@@ -1584,7 +1592,7 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
     </row>
-    <row r="7" ht="70" spans="1:23">
+    <row r="7" ht="70.75" spans="1:23">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>3</v>
@@ -1738,7 +1746,7 @@
       </c>
       <c r="M10" s="1"/>
       <c r="N10" s="1" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -299,7 +299,7 @@
     <t>Lv_Desc_Test</t>
   </si>
   <si>
-    <t>[Unit_BoneButcher,1],[Unit_RiotGuard_Lv3,2]</t>
+    <t>[Unit_BoneButcher,1],[Unit_Poacher_Lv3,2]</t>
   </si>
 </sst>
 </file>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="86">
   <si>
     <t>#</t>
   </si>
@@ -221,13 +221,22 @@
     <t>Lv_Desc_1</t>
   </si>
   <si>
-    <t>GamePhase.Invade</t>
+    <t>GamePhase.Defend</t>
   </si>
   <si>
     <t>VictoryConditionType.OccupySpecificBuildings</t>
   </si>
   <si>
     <t>FailConditionType.LoseSpecificBuildings</t>
+  </si>
+  <si>
+    <t>[Unit_HiredBodyguard,4]</t>
+  </si>
+  <si>
+    <t>[Unit_HiredBodyguard,6]</t>
+  </si>
+  <si>
+    <t>[Unit_HiredBodyguard,8]</t>
   </si>
   <si>
     <t>Lv_2</t>
@@ -1545,9 +1554,15 @@
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
+      <c r="O5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>61</v>
+      </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
     </row>
@@ -1558,22 +1573,22 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H6" s="1">
         <v>8</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>57</v>
@@ -1584,7 +1599,7 @@
       </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
@@ -1599,22 +1614,22 @@
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H7" s="1">
         <v>9</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>57</v>
@@ -1625,7 +1640,7 @@
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
@@ -1640,22 +1655,22 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H8" s="1">
         <v>6</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>57</v>
@@ -1679,22 +1694,22 @@
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H9" s="1">
         <v>6</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>57</v>
@@ -1717,25 +1732,25 @@
         <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H10" s="1">
         <v>200</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>57</v>
@@ -1746,7 +1761,7 @@
       </c>
       <c r="M10" s="1"/>
       <c r="N10" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>#</t>
   </si>
@@ -106,13 +106,16 @@
     <t>Def10Enemies</t>
   </si>
   <si>
+    <t>UnlockArchetype</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -122,7 +125,7 @@
       </rPr>
       <t>s</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -206,6 +209,9 @@
     <t>防御阶段10出怪</t>
   </si>
   <si>
+    <t>Industry unlocked on first normal clear</t>
+  </si>
+  <si>
     <t>教程关</t>
   </si>
   <si>
@@ -239,6 +245,9 @@
     <t>[Unit_HiredBodyguard,8]</t>
   </si>
   <si>
+    <t>Archetype.Sightseeing</t>
+  </si>
+  <si>
     <t>Lv_2</t>
   </si>
   <si>
@@ -257,6 +266,9 @@
     <t>[Unit_BoneButcher,1],[Unit_CanMaker_Lv3,2]</t>
   </si>
   <si>
+    <t>Archetype.Delivery</t>
+  </si>
+  <si>
     <t>Lv_3</t>
   </si>
   <si>
@@ -272,6 +284,9 @@
     <t>[Unit_BoneButcher_Lv2,1],[Unit_Intern,5]</t>
   </si>
   <si>
+    <t>Archetype.Butchery</t>
+  </si>
+  <si>
     <t>Lv_4</t>
   </si>
   <si>
@@ -281,6 +296,9 @@
     <t>Lv_Desc_4</t>
   </si>
   <si>
+    <t>Archetype.Firefighting</t>
+  </si>
+  <si>
     <t>Lv_5</t>
   </si>
   <si>
@@ -293,6 +311,9 @@
     <t>GamePhase.BuildBeforeDefend</t>
   </si>
   <si>
+    <t>Archetype.Security</t>
+  </si>
+  <si>
     <t>测试关</t>
   </si>
   <si>
@@ -309,6 +330,9 @@
   </si>
   <si>
     <t>[Unit_BoneButcher,1],[Unit_Poacher_Lv3,2]</t>
+  </si>
+  <si>
+    <t>Archetype.None</t>
   </si>
 </sst>
 </file>
@@ -798,157 +822,157 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="2" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="3" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="0" applyFont="0" fillId="2" applyFill="1" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="3" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="5" applyFill="1" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="0" applyFill="0" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="0" applyFill="0" borderId="9" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1270,7 +1294,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:X10"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
@@ -1283,7 +1307,7 @@
     <col min="11" max="13" width="17.8333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.75" spans="1:23">
+    <row r="1" ht="14.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1312,7 +1336,7 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
     </row>
-    <row r="2" ht="28.75" spans="1:23">
+    <row r="2" ht="28.75">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1380,304 +1404,322 @@
       <c r="W2" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="X2" s="0" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="3" ht="28.75" spans="1:23">
+    <row r="3" ht="28.75">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="L3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="1" t="s">
+      <c r="N3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="X3" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>29</v>
-      </c>
     </row>
-    <row r="4" ht="13" customHeight="1" spans="1:23">
+    <row r="4" ht="13" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="X4" s="0" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="5" ht="42.75" spans="1:23">
+    <row r="5" ht="42.75">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H5" s="1">
         <v>9</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
+      <c r="X5" s="0" t="s">
+        <v>64</v>
+      </c>
     </row>
-    <row r="6" ht="70.75" spans="1:23">
+    <row r="6" ht="70.75">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H6" s="1">
         <v>8</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
+      <c r="X6" s="0" t="s">
+        <v>71</v>
+      </c>
     </row>
-    <row r="7" ht="70.75" spans="1:23">
+    <row r="7" ht="70.75">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H7" s="1">
         <v>9</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
+      <c r="X7" s="0" t="s">
+        <v>77</v>
+      </c>
     </row>
-    <row r="8" ht="42.75" spans="1:23">
+    <row r="8" ht="42.75">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H8" s="1">
         <v>6</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
@@ -1686,37 +1728,40 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
+      <c r="X8" s="0" t="s">
+        <v>81</v>
+      </c>
     </row>
-    <row r="9" ht="42.75" spans="1:23">
+    <row r="9" ht="42.75">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>5</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H9" s="1">
         <v>6</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
@@ -1725,49 +1770,55 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
+      <c r="X9" s="0" t="s">
+        <v>86</v>
+      </c>
     </row>
-    <row r="10" ht="70.75" spans="1:23">
+    <row r="10" ht="70.75">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H10" s="1">
         <v>200</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M10" s="1"/>
       <c r="N10" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
+      <c r="X10" s="0" t="s">
+        <v>93</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAAGameData/DataTables/LevelTable.xlsx
+++ b/AAAGameData/DataTables/LevelTable.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="122">
   <si>
     <t>#</t>
   </si>
@@ -109,13 +109,16 @@
     <t>UnlockArchetype</t>
   </si>
   <si>
+    <t>DefaultArchetype</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -125,7 +128,7 @@
       </rPr>
       <t>s</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
@@ -209,7 +212,10 @@
     <t>防御阶段10出怪</t>
   </si>
   <si>
-    <t>Industry unlocked on first normal clear</t>
+    <t>首通解锁行业</t>
+  </si>
+  <si>
+    <t>默认初始行业</t>
   </si>
   <si>
     <t>教程关</t>
@@ -245,73 +251,154 @@
     <t>[Unit_HiredBodyguard,8]</t>
   </si>
   <si>
+    <t>Archetype.Coding</t>
+  </si>
+  <si>
+    <t>Lv_2</t>
+  </si>
+  <si>
+    <t>Level/Level_2</t>
+  </si>
+  <si>
+    <t>Lv_Name_2</t>
+  </si>
+  <si>
+    <t>Lv_Desc_2</t>
+  </si>
+  <si>
+    <t>GamePhase.BuildBeforeInvade</t>
+  </si>
+  <si>
+    <t>[Unit_BoneButcher,1],[Unit_CanMaker_Lv3,2]</t>
+  </si>
+  <si>
     <t>Archetype.Sightseeing</t>
   </si>
   <si>
-    <t>Lv_2</t>
-  </si>
-  <si>
-    <t>Level/Level_2</t>
-  </si>
-  <si>
-    <t>Lv_Name_2</t>
-  </si>
-  <si>
-    <t>Lv_Desc_2</t>
-  </si>
-  <si>
-    <t>GamePhase.BuildBeforeInvade</t>
-  </si>
-  <si>
-    <t>[Unit_BoneButcher,1],[Unit_CanMaker_Lv3,2]</t>
+    <t>Lv_3</t>
+  </si>
+  <si>
+    <t>Level/Level_3</t>
+  </si>
+  <si>
+    <t>Lv_Name_3</t>
+  </si>
+  <si>
+    <t>Lv_Desc_3</t>
+  </si>
+  <si>
+    <t>[Unit_BoneButcher_Lv2,1],[Unit_Intern,5]</t>
   </si>
   <si>
     <t>Archetype.Delivery</t>
   </si>
   <si>
-    <t>Lv_3</t>
-  </si>
-  <si>
-    <t>Level/Level_3</t>
-  </si>
-  <si>
-    <t>Lv_Name_3</t>
-  </si>
-  <si>
-    <t>Lv_Desc_3</t>
-  </si>
-  <si>
-    <t>[Unit_BoneButcher_Lv2,1],[Unit_Intern,5]</t>
+    <t>Lv_4</t>
+  </si>
+  <si>
+    <t>Level/Level_4</t>
+  </si>
+  <si>
+    <t>Lv_Name_4</t>
+  </si>
+  <si>
+    <t>Lv_Desc_4</t>
+  </si>
+  <si>
+    <t>Archetype.Firefighting</t>
+  </si>
+  <si>
+    <t>Lv_5</t>
+  </si>
+  <si>
+    <t>Level/Level_5</t>
+  </si>
+  <si>
+    <t>Lv_Name_5</t>
+  </si>
+  <si>
+    <t>Lv_Desc_5</t>
+  </si>
+  <si>
+    <t>GamePhase.BuildBeforeDefend</t>
+  </si>
+  <si>
+    <t>Archetype.Security</t>
+  </si>
+  <si>
+    <t>Lv_6</t>
+  </si>
+  <si>
+    <t>Level/Level_6</t>
+  </si>
+  <si>
+    <t>Lv_Name_6</t>
+  </si>
+  <si>
+    <t>Lv_Desc_6</t>
+  </si>
+  <si>
+    <t>Archetype.Hunting</t>
+  </si>
+  <si>
+    <t>Lv_7</t>
+  </si>
+  <si>
+    <t>Level/Level_7</t>
+  </si>
+  <si>
+    <t>Lv_Name_7</t>
+  </si>
+  <si>
+    <t>Lv_Desc_7</t>
   </si>
   <si>
     <t>Archetype.Butchery</t>
   </si>
   <si>
-    <t>Lv_4</t>
-  </si>
-  <si>
-    <t>Lv_Name_4</t>
-  </si>
-  <si>
-    <t>Lv_Desc_4</t>
-  </si>
-  <si>
-    <t>Archetype.Firefighting</t>
-  </si>
-  <si>
-    <t>Lv_5</t>
-  </si>
-  <si>
-    <t>Lv_Name_5</t>
-  </si>
-  <si>
-    <t>Lv_Desc_5</t>
-  </si>
-  <si>
-    <t>GamePhase.BuildBeforeDefend</t>
-  </si>
-  <si>
-    <t>Archetype.Security</t>
+    <t>Lv_8</t>
+  </si>
+  <si>
+    <t>Level/Level_8</t>
+  </si>
+  <si>
+    <t>Lv_Name_8</t>
+  </si>
+  <si>
+    <t>Lv_Desc_8</t>
+  </si>
+  <si>
+    <t>Archetype.Medical,Archetype.Sports</t>
+  </si>
+  <si>
+    <t>Lv_9</t>
+  </si>
+  <si>
+    <t>Level/Level_9</t>
+  </si>
+  <si>
+    <t>Lv_Name_9</t>
+  </si>
+  <si>
+    <t>Lv_Desc_9</t>
+  </si>
+  <si>
+    <t>Archetype.Gardening</t>
+  </si>
+  <si>
+    <t>Archetype.Medical</t>
+  </si>
+  <si>
+    <t>Lv_10</t>
+  </si>
+  <si>
+    <t>Level/Level_10</t>
+  </si>
+  <si>
+    <t>Lv_Name_10</t>
+  </si>
+  <si>
+    <t>Lv_Desc_10</t>
   </si>
   <si>
     <t>测试关</t>
@@ -330,9 +417,6 @@
   </si>
   <si>
     <t>[Unit_BoneButcher,1],[Unit_Poacher_Lv3,2]</t>
-  </si>
-  <si>
-    <t>Archetype.None</t>
   </si>
 </sst>
 </file>
@@ -822,157 +906,157 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="2" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="3" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="0" applyFont="0" fillId="2" applyFill="1" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="3" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="5" applyFill="1" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="0" applyFill="0" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="0" applyFill="0" borderId="9" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1294,7 +1378,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X10"/>
+  <dimension ref="A1:Y15"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
@@ -1307,7 +1391,7 @@
     <col min="11" max="13" width="17.8333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.75">
+    <row r="1" ht="14.75" spans="1:25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1335,8 +1419,14 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
     </row>
-    <row r="2" ht="28.75">
+    <row r="2" ht="28.75" spans="1:25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1404,322 +1494,350 @@
       <c r="W2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="0" t="s">
+      <c r="X2" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="Y2" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="3" ht="28.75">
+    <row r="3" ht="28.75" spans="1:25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="L3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="1" t="s">
+      <c r="N3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="X3" s="0" t="s">
-        <v>28</v>
-      </c>
     </row>
-    <row r="4" ht="13" customHeight="1">
+    <row r="4" ht="13" customHeight="1" spans="1:25">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="X4" s="0" t="s">
         <v>52</v>
       </c>
+      <c r="X4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="5" ht="42.75">
+    <row r="5" ht="42.75" spans="1:25">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H5" s="1">
         <v>9</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
-      <c r="X5" s="0" t="s">
-        <v>64</v>
-      </c>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y5" s="1"/>
     </row>
-    <row r="6" ht="70.75">
+    <row r="6" ht="70.75" spans="1:25">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>2</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H6" s="1">
         <v>8</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
-      <c r="X6" s="0" t="s">
-        <v>71</v>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
-    <row r="7" ht="70.75">
+    <row r="7" ht="70.75" spans="1:25">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H7" s="1">
         <v>9</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
-      <c r="X7" s="0" t="s">
-        <v>77</v>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="8" ht="42.75">
+    <row r="8" ht="42.75" spans="1:25">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H8" s="1">
         <v>6</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
@@ -1728,40 +1846,47 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
-      <c r="X8" s="0" t="s">
-        <v>81</v>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="9" ht="42.75">
+    <row r="9" ht="42.75" spans="1:25">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>5</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H9" s="1">
         <v>6</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
@@ -1770,54 +1895,301 @@
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
-      <c r="X9" s="0" t="s">
-        <v>86</v>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y9" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="10" ht="70.75">
+    <row r="10" ht="42.75" spans="1:25">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>6</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H10" s="1">
+        <v>6</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H10" s="1">
-        <v>200</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="J10" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M10" s="1"/>
-      <c r="N10" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
-      <c r="X10" s="0" t="s">
-        <v>93</v>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" ht="42.75" spans="1:25">
+      <c r="B11" s="1">
+        <v>7</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H11" s="1">
+        <v>6</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" ht="56.75" spans="1:25">
+      <c r="B12" s="1">
+        <v>8</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H12" s="1">
+        <v>6</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" ht="42" spans="1:25">
+      <c r="B13" s="1">
+        <v>9</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H13" s="1">
+        <v>6</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" ht="42.75" spans="1:25">
+      <c r="B14" s="1">
+        <v>10</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H14" s="1">
+        <v>6</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
+      <c r="X14" s="1"/>
+      <c r="Y14" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" ht="70.75" spans="1:25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H15" s="1">
+        <v>200</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1"/>
+      <c r="Y15" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
